--- a/tame_output/ON/bt/strategyON_20231128.xlsx
+++ b/tame_output/ON/bt/strategyON_20231128.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.3%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>22.8%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.4%</t>
+          <t>453.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>102.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>132.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>126.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1794"/>
+  <dimension ref="A1:G1795"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42772,7 +42772,7 @@
         <v>45256</v>
       </c>
       <c r="B1794" t="n">
-        <v>3.145119495204679</v>
+        <v>3.147014107714842</v>
       </c>
       <c r="C1794" t="n">
         <v>3.076099785321473</v>
@@ -42788,6 +42788,29 @@
       </c>
       <c r="G1794" t="n">
         <v>4.387384067580576</v>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" s="2" t="n">
+        <v>45257</v>
+      </c>
+      <c r="B1795" t="n">
+        <v>3.139561641237695</v>
+      </c>
+      <c r="C1795" t="n">
+        <v>3.082620445523309</v>
+      </c>
+      <c r="D1795" t="n">
+        <v>1.563294493921939</v>
+      </c>
+      <c r="E1795" t="n">
+        <v>3.707581818778338</v>
+      </c>
+      <c r="F1795" t="n">
+        <v>2.185590138912724</v>
+      </c>
+      <c r="G1795" t="n">
+        <v>4.393974528870945</v>
       </c>
     </row>
   </sheetData>
